--- a/data/output/stock.xlsx
+++ b/data/output/stock.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15920" activeTab="1"/>
+    <workbookView windowHeight="15920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1000,11 +999,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -1545,157 +1544,157 @@
   <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="17" spans="1:25">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="17" spans="1:25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="84" spans="1:25">
-      <c r="A2" s="1" t="s">
+    <row r="2" s="2" customFormat="1" ht="84" spans="1:25">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="2" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1993,85 +1992,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Y3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
-  <cols>
-    <col min="2" max="2" width="10.3076923076923" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-    </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/data/output/stock.xlsx
+++ b/data/output/stock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15920"/>
+    <workbookView windowHeight="19680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,10 +29,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="115">
   <si>
-    <t>股票编号</t>
-  </si>
-  <si>
-    <t>股票名称</t>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>名称</t>
   </si>
   <si>
     <t>持有</t>

--- a/data/output/stock.xlsx
+++ b/data/output/stock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="19680"/>
+    <workbookView windowHeight="23840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
     <t>MA-Week-20 首次突破 MA-Week-60</t>
   </si>
   <si>
-    <t>Stock-Low 站上 MA-Month-31 线</t>
+    <t>Stock-Low 站上 MA-Month-30 线</t>
   </si>
   <si>
     <t>MA-Week-30 首次突破 MA-Week-60</t>
@@ -999,8 +999,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1542,9 +1542,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y37"/>
-  <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="13.6923076923077" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="16384" width="13.6923076923077" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17" spans="1:25">
+    <row r="1" s="1" customFormat="1" ht="34" spans="1:25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>

--- a/data/output/stock.xlsx
+++ b/data/output/stock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23840"/>
+    <workbookView windowHeight="15920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
   <si>
     <t>编号</t>
   </si>
@@ -86,6 +86,12 @@
     <t>下降趋势 4-1</t>
   </si>
   <si>
+    <t>周期 1-1</t>
+  </si>
+  <si>
+    <t>周期 2-1</t>
+  </si>
+  <si>
     <t>小调整 1-1</t>
   </si>
   <si>
@@ -144,6 +150,12 @@
   </si>
   <si>
     <t>Stock-Low 下穿跌破 MA-Month-30 线</t>
+  </si>
+  <si>
+    <t>跌破 250 日</t>
+  </si>
+  <si>
+    <t>跌破 250 周</t>
   </si>
   <si>
     <t>MACD-Month 月小坑</t>
@@ -1541,13 +1553,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr defaultColWidth="13.6923076923077" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="16384" width="13.6923076923077" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="34" spans="1:25">
+    <row r="1" s="1" customFormat="1" ht="17" spans="1:27">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1623,8 +1635,14 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="84" spans="1:25">
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="68" spans="1:27">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1632,7 +1650,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>3</v>
@@ -1641,72 +1659,78 @@
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>46</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -1719,276 +1743,276 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:27">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/stock.xlsx
+++ b/data/output/stock.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="15920"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="stock" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -176,211 +176,211 @@
     <t>策略分类-底部信号-Boll月线下轨+季线中下轨</t>
   </si>
   <si>
-    <t>sh600025</t>
+    <t>600025</t>
   </si>
   <si>
     <t>华能水电</t>
   </si>
   <si>
-    <t>sh600028</t>
+    <t>600028</t>
   </si>
   <si>
     <t>中国石化</t>
   </si>
   <si>
-    <t>sh600036</t>
+    <t>600036</t>
   </si>
   <si>
     <t>招商银行</t>
   </si>
   <si>
-    <t>sh600096</t>
+    <t>600096</t>
   </si>
   <si>
     <t>云天化</t>
   </si>
   <si>
-    <t>sh600309</t>
+    <t>600309</t>
   </si>
   <si>
     <t>万华化学</t>
   </si>
   <si>
-    <t>sh600519</t>
+    <t>600519</t>
   </si>
   <si>
     <t>贵州茅台</t>
   </si>
   <si>
-    <t>sh600600</t>
+    <t>600600</t>
   </si>
   <si>
     <t>青岛啤酒</t>
   </si>
   <si>
-    <t>sh600690</t>
+    <t>600690</t>
   </si>
   <si>
     <t>海尔智家</t>
   </si>
   <si>
-    <t>sh600795</t>
+    <t>600795</t>
   </si>
   <si>
     <t>国电电力</t>
   </si>
   <si>
-    <t>sh600886</t>
+    <t>600886</t>
   </si>
   <si>
     <t>国投电力</t>
   </si>
   <si>
-    <t>sh600887</t>
+    <t>600887</t>
   </si>
   <si>
     <t>伊利股份</t>
   </si>
   <si>
-    <t>sh600900</t>
+    <t>600900</t>
   </si>
   <si>
     <t>长江电力</t>
   </si>
   <si>
-    <t>sh600938</t>
+    <t>600938</t>
   </si>
   <si>
     <t>中国海油</t>
   </si>
   <si>
-    <t>sh600941</t>
+    <t>600941</t>
   </si>
   <si>
     <t>中国移动</t>
   </si>
   <si>
-    <t>sh601066</t>
+    <t>601066</t>
   </si>
   <si>
     <t>中信建投</t>
   </si>
   <si>
-    <t>sh601088</t>
+    <t>601088</t>
   </si>
   <si>
     <t>中国神华</t>
   </si>
   <si>
-    <t>sh601288</t>
+    <t>601288</t>
   </si>
   <si>
     <t>农业银行</t>
   </si>
   <si>
-    <t>sh601318</t>
+    <t>601318</t>
   </si>
   <si>
     <t>中国平安</t>
   </si>
   <si>
-    <t>sh601328</t>
+    <t>601328</t>
   </si>
   <si>
     <t>交通银行</t>
   </si>
   <si>
-    <t>sh601398</t>
+    <t>601398</t>
   </si>
   <si>
     <t>工商银行</t>
   </si>
   <si>
-    <t>sh601601</t>
+    <t>601601</t>
   </si>
   <si>
     <t>中国太保</t>
   </si>
   <si>
-    <t>sh601658</t>
+    <t>601658</t>
   </si>
   <si>
     <t>邮储银行</t>
   </si>
   <si>
-    <t>sh601728</t>
+    <t>601728</t>
   </si>
   <si>
     <t>中国电信</t>
   </si>
   <si>
-    <t>sh601857</t>
+    <t>601857</t>
   </si>
   <si>
     <t>中国石油</t>
   </si>
   <si>
-    <t>sh601919</t>
+    <t>601919</t>
   </si>
   <si>
     <t>中远海控</t>
   </si>
   <si>
-    <t>sh601939</t>
+    <t>601939</t>
   </si>
   <si>
     <t>建设银行</t>
   </si>
   <si>
-    <t>sh601985</t>
+    <t>601985</t>
   </si>
   <si>
     <t>中国核电</t>
   </si>
   <si>
-    <t>sh601988</t>
+    <t>601988</t>
   </si>
   <si>
     <t>中国银行</t>
   </si>
   <si>
-    <t>sz000333</t>
+    <t>000333</t>
   </si>
   <si>
     <t>美的集团</t>
   </si>
   <si>
-    <t>sz000538</t>
+    <t>000538</t>
   </si>
   <si>
     <t>云南白药</t>
   </si>
   <si>
-    <t>sz000568</t>
+    <t>000568</t>
   </si>
   <si>
     <t>泸州老窖</t>
   </si>
   <si>
-    <t>sz000651</t>
+    <t>000651</t>
   </si>
   <si>
     <t>格力电器</t>
   </si>
   <si>
-    <t>sz000858</t>
+    <t>000858</t>
   </si>
   <si>
     <t>五粮液</t>
   </si>
   <si>
-    <t>sz002142</t>
+    <t>002142</t>
   </si>
   <si>
     <t>宁波银行</t>
   </si>
   <si>
-    <t>sz003816</t>
+    <t>003816</t>
   </si>
   <si>
     <t>中国广核</t>
@@ -396,16 +396,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+  <fonts count="20">
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -859,9 +851,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -877,149 +867,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1072,221 +1051,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1296,7 +1061,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1306,39 +1071,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1370,7 +1135,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1405,7 +1169,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1417,131 +1180,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1554,174 +1346,171 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultColWidth="13.6923076923077" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="1" max="16384" width="13.6923076923077" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17" spans="1:27">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:27">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="68" spans="1:27">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:27">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>40</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" t="s">
         <v>41</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" t="s">
         <v>42</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" t="s">
         <v>43</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" t="s">
         <v>47</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1732,16 +1521,6 @@
       <c r="B3" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:27">
       <c r="A4" t="s">
@@ -2016,7 +1795,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>